--- a/output/pdf_financials_xlsx/VSBY.xlsx
+++ b/output/pdf_financials_xlsx/VSBY.xlsx
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>10.483287</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>10.758095</v>
       </c>
     </row>
     <row r="93">
@@ -2878,7 +2878,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>10.483287</v>
       </c>

--- a/output/pdf_financials_xlsx/VSBY.xlsx
+++ b/output/pdf_financials_xlsx/VSBY.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.030927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004108</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.374871</v>
+        <v>-12.405798</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-11.50239</v>
+        <v>-11.506498</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-12.245507</v>
+        <v>-12.276434</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-11.365987</v>
+        <v>-11.370095</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-605.1954707850214</v>
+        <v>-606.7239399880498</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1307.009169543409</v>
+        <v>-1307.481560869255</v>
       </c>
     </row>
     <row r="31">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.064225</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.05418</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.064225</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.05418</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.613855</v>
+        <v>0.54963</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.214472</v>
+        <v>0.160292</v>
       </c>
     </row>
     <row r="49">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.105644</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064454</v>
       </c>
     </row>
     <row r="125">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.105644</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064454</v>
       </c>
     </row>
     <row r="126">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3726,7 +3726,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.105644</v>
       </c>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">

--- a/output/pdf_financials_xlsx/VSBY.xlsx
+++ b/output/pdf_financials_xlsx/VSBY.xlsx
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.346367</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.402765</v>
       </c>
     </row>
     <row r="68">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.004249</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060845</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003451</v>
       </c>
     </row>
     <row r="112">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060845</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003451</v>
       </c>
     </row>
     <row r="135">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-10.582861</v>
+        <v>-10.643706</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.652637</v>
+        <v>-4.656088</v>
       </c>
     </row>
   </sheetData>
@@ -3098,7 +3098,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.004249</v>
       </c>
@@ -3574,7 +3578,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>-0.060845</v>
       </c>
